--- a/frontend/selenium-tests/selenium-test-report.xlsx
+++ b/frontend/selenium-tests/selenium-test-report.xlsx
@@ -38,7 +38,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>24/7/2026, 6:17:22 pm</t>
+    <t>24/7/2026, 6:59:12 pm</t>
   </si>
   <si>
     <t>Browser Environment</t>
@@ -3183,7 +3183,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="7">
-        <v>1041</v>
+        <v>315</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>17</v>
@@ -3221,7 +3221,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="9">
-        <v>958</v>
+        <v>469</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>17</v>
@@ -3259,7 +3259,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="7">
-        <v>872</v>
+        <v>845</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>17</v>
@@ -3297,7 +3297,7 @@
         <v>50</v>
       </c>
       <c r="K5" s="9">
-        <v>828</v>
+        <v>414</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>17</v>
@@ -3335,7 +3335,7 @@
         <v>55</v>
       </c>
       <c r="K6" s="7">
-        <v>944</v>
+        <v>169</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>17</v>
@@ -3373,7 +3373,7 @@
         <v>60</v>
       </c>
       <c r="K7" s="9">
-        <v>278</v>
+        <v>472</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>17</v>
@@ -3411,7 +3411,7 @@
         <v>50</v>
       </c>
       <c r="K8" s="7">
-        <v>585</v>
+        <v>314</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>17</v>
@@ -3449,7 +3449,7 @@
         <v>55</v>
       </c>
       <c r="K9" s="9">
-        <v>162</v>
+        <v>624</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>17</v>
@@ -3487,7 +3487,7 @@
         <v>60</v>
       </c>
       <c r="K10" s="7">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>17</v>
@@ -3525,7 +3525,7 @@
         <v>50</v>
       </c>
       <c r="K11" s="9">
-        <v>464</v>
+        <v>943</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>17</v>
@@ -3563,7 +3563,7 @@
         <v>55</v>
       </c>
       <c r="K12" s="7">
-        <v>1010</v>
+        <v>771</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>17</v>
@@ -3601,7 +3601,7 @@
         <v>60</v>
       </c>
       <c r="K13" s="9">
-        <v>786</v>
+        <v>687</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>17</v>
@@ -3639,7 +3639,7 @@
         <v>50</v>
       </c>
       <c r="K14" s="7">
-        <v>264</v>
+        <v>715</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>17</v>
@@ -3677,7 +3677,7 @@
         <v>55</v>
       </c>
       <c r="K15" s="9">
-        <v>953</v>
+        <v>723</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>17</v>
@@ -3715,7 +3715,7 @@
         <v>60</v>
       </c>
       <c r="K16" s="7">
-        <v>245</v>
+        <v>754</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>17</v>
@@ -3753,7 +3753,7 @@
         <v>50</v>
       </c>
       <c r="K17" s="9">
-        <v>1030</v>
+        <v>220</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>17</v>
@@ -3791,7 +3791,7 @@
         <v>55</v>
       </c>
       <c r="K18" s="7">
-        <v>375</v>
+        <v>791</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>17</v>
@@ -3829,7 +3829,7 @@
         <v>60</v>
       </c>
       <c r="K19" s="9">
-        <v>921</v>
+        <v>883</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>17</v>
@@ -3867,7 +3867,7 @@
         <v>50</v>
       </c>
       <c r="K20" s="7">
-        <v>756</v>
+        <v>1007</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>17</v>
@@ -3905,7 +3905,7 @@
         <v>55</v>
       </c>
       <c r="K21" s="9">
-        <v>817</v>
+        <v>605</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>17</v>
@@ -3943,7 +3943,7 @@
         <v>60</v>
       </c>
       <c r="K22" s="7">
-        <v>615</v>
+        <v>453</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>17</v>
@@ -3981,7 +3981,7 @@
         <v>50</v>
       </c>
       <c r="K23" s="9">
-        <v>489</v>
+        <v>609</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>17</v>
@@ -4019,7 +4019,7 @@
         <v>55</v>
       </c>
       <c r="K24" s="7">
-        <v>659</v>
+        <v>685</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>17</v>
@@ -4057,7 +4057,7 @@
         <v>60</v>
       </c>
       <c r="K25" s="9">
-        <v>317</v>
+        <v>850</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>17</v>
@@ -4095,7 +4095,7 @@
         <v>50</v>
       </c>
       <c r="K26" s="7">
-        <v>566</v>
+        <v>951</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>17</v>
@@ -4133,7 +4133,7 @@
         <v>55</v>
       </c>
       <c r="K27" s="9">
-        <v>528</v>
+        <v>403</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>17</v>
@@ -4171,7 +4171,7 @@
         <v>60</v>
       </c>
       <c r="K28" s="7">
-        <v>374</v>
+        <v>919</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>17</v>
@@ -4209,7 +4209,7 @@
         <v>50</v>
       </c>
       <c r="K29" s="9">
-        <v>667</v>
+        <v>765</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>17</v>
@@ -4247,7 +4247,7 @@
         <v>55</v>
       </c>
       <c r="K30" s="7">
-        <v>497</v>
+        <v>206</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>17</v>
@@ -4285,7 +4285,7 @@
         <v>60</v>
       </c>
       <c r="K31" s="9">
-        <v>708</v>
+        <v>203</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>17</v>
@@ -4323,7 +4323,7 @@
         <v>50</v>
       </c>
       <c r="K32" s="7">
-        <v>484</v>
+        <v>295</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>17</v>
@@ -4361,7 +4361,7 @@
         <v>55</v>
       </c>
       <c r="K33" s="9">
-        <v>332</v>
+        <v>760</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>17</v>
@@ -4399,7 +4399,7 @@
         <v>60</v>
       </c>
       <c r="K34" s="7">
-        <v>445</v>
+        <v>649</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>17</v>
@@ -4437,7 +4437,7 @@
         <v>50</v>
       </c>
       <c r="K35" s="9">
-        <v>545</v>
+        <v>804</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>17</v>
@@ -4475,7 +4475,7 @@
         <v>55</v>
       </c>
       <c r="K36" s="7">
-        <v>504</v>
+        <v>685</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>17</v>
@@ -4513,7 +4513,7 @@
         <v>60</v>
       </c>
       <c r="K37" s="9">
-        <v>581</v>
+        <v>313</v>
       </c>
       <c r="L37" s="8" t="s">
         <v>17</v>
@@ -4551,7 +4551,7 @@
         <v>50</v>
       </c>
       <c r="K38" s="7">
-        <v>907</v>
+        <v>800</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>17</v>
@@ -4589,7 +4589,7 @@
         <v>55</v>
       </c>
       <c r="K39" s="9">
-        <v>1005</v>
+        <v>742</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>17</v>
@@ -4627,7 +4627,7 @@
         <v>60</v>
       </c>
       <c r="K40" s="7">
-        <v>455</v>
+        <v>900</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>17</v>
@@ -4665,7 +4665,7 @@
         <v>50</v>
       </c>
       <c r="K41" s="9">
-        <v>295</v>
+        <v>602</v>
       </c>
       <c r="L41" s="8" t="s">
         <v>17</v>
@@ -4703,7 +4703,7 @@
         <v>55</v>
       </c>
       <c r="K42" s="7">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>17</v>
@@ -4741,7 +4741,7 @@
         <v>60</v>
       </c>
       <c r="K43" s="9">
-        <v>203</v>
+        <v>469</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>17</v>
@@ -4779,7 +4779,7 @@
         <v>50</v>
       </c>
       <c r="K44" s="7">
-        <v>257</v>
+        <v>320</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>17</v>
@@ -4817,7 +4817,7 @@
         <v>55</v>
       </c>
       <c r="K45" s="9">
-        <v>536</v>
+        <v>973</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>17</v>
@@ -4855,7 +4855,7 @@
         <v>60</v>
       </c>
       <c r="K46" s="7">
-        <v>895</v>
+        <v>164</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>17</v>
@@ -4893,7 +4893,7 @@
         <v>50</v>
       </c>
       <c r="K47" s="9">
-        <v>740</v>
+        <v>977</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>17</v>
@@ -4931,7 +4931,7 @@
         <v>55</v>
       </c>
       <c r="K48" s="7">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="L48" s="10" t="s">
         <v>189</v>
@@ -4969,7 +4969,7 @@
         <v>60</v>
       </c>
       <c r="K49" s="9">
-        <v>874</v>
+        <v>959</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>17</v>
@@ -5007,7 +5007,7 @@
         <v>50</v>
       </c>
       <c r="K50" s="7">
-        <v>756</v>
+        <v>916</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>17</v>
@@ -5045,7 +5045,7 @@
         <v>55</v>
       </c>
       <c r="K51" s="9">
-        <v>656</v>
+        <v>227</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>17</v>
@@ -5083,7 +5083,7 @@
         <v>60</v>
       </c>
       <c r="K52" s="7">
-        <v>782</v>
+        <v>723</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>17</v>
@@ -5121,7 +5121,7 @@
         <v>50</v>
       </c>
       <c r="K53" s="9">
-        <v>681</v>
+        <v>915</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>17</v>
@@ -5159,7 +5159,7 @@
         <v>55</v>
       </c>
       <c r="K54" s="7">
-        <v>636</v>
+        <v>568</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>17</v>
@@ -5197,7 +5197,7 @@
         <v>60</v>
       </c>
       <c r="K55" s="9">
-        <v>659</v>
+        <v>898</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>17</v>
@@ -5235,7 +5235,7 @@
         <v>50</v>
       </c>
       <c r="K56" s="7">
-        <v>400</v>
+        <v>846</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>17</v>
@@ -5273,7 +5273,7 @@
         <v>55</v>
       </c>
       <c r="K57" s="9">
-        <v>730</v>
+        <v>433</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>17</v>
@@ -5311,7 +5311,7 @@
         <v>60</v>
       </c>
       <c r="K58" s="7">
-        <v>584</v>
+        <v>843</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>17</v>
@@ -5349,7 +5349,7 @@
         <v>50</v>
       </c>
       <c r="K59" s="9">
-        <v>392</v>
+        <v>777</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>17</v>
@@ -5387,7 +5387,7 @@
         <v>55</v>
       </c>
       <c r="K60" s="7">
-        <v>439</v>
+        <v>753</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>17</v>
@@ -5425,7 +5425,7 @@
         <v>60</v>
       </c>
       <c r="K61" s="9">
-        <v>973</v>
+        <v>319</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>17</v>
@@ -5463,7 +5463,7 @@
         <v>50</v>
       </c>
       <c r="K62" s="7">
-        <v>791</v>
+        <v>461</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>17</v>
@@ -5501,7 +5501,7 @@
         <v>55</v>
       </c>
       <c r="K63" s="9">
-        <v>561</v>
+        <v>325</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>17</v>
@@ -5539,7 +5539,7 @@
         <v>60</v>
       </c>
       <c r="K64" s="7">
-        <v>222</v>
+        <v>596</v>
       </c>
       <c r="L64" s="8" t="s">
         <v>17</v>
@@ -5577,7 +5577,7 @@
         <v>50</v>
       </c>
       <c r="K65" s="9">
-        <v>905</v>
+        <v>203</v>
       </c>
       <c r="L65" s="8" t="s">
         <v>17</v>
@@ -5615,7 +5615,7 @@
         <v>55</v>
       </c>
       <c r="K66" s="7">
-        <v>966</v>
+        <v>712</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>17</v>
@@ -5653,7 +5653,7 @@
         <v>60</v>
       </c>
       <c r="K67" s="9">
-        <v>500</v>
+        <v>437</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>17</v>
@@ -5691,7 +5691,7 @@
         <v>50</v>
       </c>
       <c r="K68" s="7">
-        <v>861</v>
+        <v>1035</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>17</v>
@@ -5729,7 +5729,7 @@
         <v>55</v>
       </c>
       <c r="K69" s="9">
-        <v>240</v>
+        <v>283</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>17</v>
@@ -5767,7 +5767,7 @@
         <v>60</v>
       </c>
       <c r="K70" s="7">
-        <v>627</v>
+        <v>1006</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>17</v>
@@ -5805,7 +5805,7 @@
         <v>50</v>
       </c>
       <c r="K71" s="9">
-        <v>604</v>
+        <v>159</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>17</v>
@@ -5843,7 +5843,7 @@
         <v>55</v>
       </c>
       <c r="K72" s="7">
-        <v>284</v>
+        <v>189</v>
       </c>
       <c r="L72" s="8" t="s">
         <v>17</v>
@@ -5881,7 +5881,7 @@
         <v>60</v>
       </c>
       <c r="K73" s="9">
-        <v>163</v>
+        <v>550</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>17</v>
@@ -5919,7 +5919,7 @@
         <v>50</v>
       </c>
       <c r="K74" s="7">
-        <v>896</v>
+        <v>311</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>17</v>
@@ -5957,7 +5957,7 @@
         <v>55</v>
       </c>
       <c r="K75" s="9">
-        <v>354</v>
+        <v>612</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>17</v>
@@ -5995,7 +5995,7 @@
         <v>60</v>
       </c>
       <c r="K76" s="7">
-        <v>268</v>
+        <v>705</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>17</v>
@@ -6033,7 +6033,7 @@
         <v>50</v>
       </c>
       <c r="K77" s="9">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>17</v>
@@ -6071,7 +6071,7 @@
         <v>55</v>
       </c>
       <c r="K78" s="7">
-        <v>814</v>
+        <v>912</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>17</v>
@@ -6109,7 +6109,7 @@
         <v>60</v>
       </c>
       <c r="K79" s="9">
-        <v>790</v>
+        <v>618</v>
       </c>
       <c r="L79" s="8" t="s">
         <v>17</v>
@@ -6147,7 +6147,7 @@
         <v>50</v>
       </c>
       <c r="K80" s="7">
-        <v>150</v>
+        <v>936</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>17</v>
@@ -6185,7 +6185,7 @@
         <v>55</v>
       </c>
       <c r="K81" s="9">
-        <v>702</v>
+        <v>965</v>
       </c>
       <c r="L81" s="8" t="s">
         <v>17</v>
@@ -6223,7 +6223,7 @@
         <v>60</v>
       </c>
       <c r="K82" s="7">
-        <v>951</v>
+        <v>758</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>17</v>
@@ -6261,7 +6261,7 @@
         <v>50</v>
       </c>
       <c r="K83" s="9">
-        <v>786</v>
+        <v>698</v>
       </c>
       <c r="L83" s="8" t="s">
         <v>17</v>
@@ -6299,7 +6299,7 @@
         <v>55</v>
       </c>
       <c r="K84" s="7">
-        <v>153</v>
+        <v>529</v>
       </c>
       <c r="L84" s="11" t="s">
         <v>267</v>
@@ -6337,7 +6337,7 @@
         <v>60</v>
       </c>
       <c r="K85" s="9">
-        <v>772</v>
+        <v>340</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>17</v>
@@ -6375,7 +6375,7 @@
         <v>50</v>
       </c>
       <c r="K86" s="7">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>17</v>
@@ -6413,7 +6413,7 @@
         <v>55</v>
       </c>
       <c r="K87" s="9">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>17</v>
@@ -6451,7 +6451,7 @@
         <v>60</v>
       </c>
       <c r="K88" s="7">
-        <v>444</v>
+        <v>498</v>
       </c>
       <c r="L88" s="8" t="s">
         <v>17</v>
@@ -6489,7 +6489,7 @@
         <v>50</v>
       </c>
       <c r="K89" s="9">
-        <v>957</v>
+        <v>168</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>17</v>
@@ -6527,7 +6527,7 @@
         <v>55</v>
       </c>
       <c r="K90" s="7">
-        <v>704</v>
+        <v>335</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>17</v>
@@ -6565,7 +6565,7 @@
         <v>60</v>
       </c>
       <c r="K91" s="9">
-        <v>579</v>
+        <v>814</v>
       </c>
       <c r="L91" s="8" t="s">
         <v>17</v>
@@ -6603,7 +6603,7 @@
         <v>50</v>
       </c>
       <c r="K92" s="7">
-        <v>728</v>
+        <v>744</v>
       </c>
       <c r="L92" s="8" t="s">
         <v>17</v>
@@ -6641,7 +6641,7 @@
         <v>55</v>
       </c>
       <c r="K93" s="9">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="L93" s="8" t="s">
         <v>17</v>
@@ -6679,7 +6679,7 @@
         <v>60</v>
       </c>
       <c r="K94" s="7">
-        <v>159</v>
+        <v>548</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>17</v>
@@ -6717,7 +6717,7 @@
         <v>50</v>
       </c>
       <c r="K95" s="9">
-        <v>725</v>
+        <v>651</v>
       </c>
       <c r="L95" s="10" t="s">
         <v>189</v>
@@ -6755,7 +6755,7 @@
         <v>55</v>
       </c>
       <c r="K96" s="7">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>17</v>
@@ -6793,7 +6793,7 @@
         <v>60</v>
       </c>
       <c r="K97" s="9">
-        <v>413</v>
+        <v>264</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>17</v>
@@ -6831,7 +6831,7 @@
         <v>50</v>
       </c>
       <c r="K98" s="7">
-        <v>574</v>
+        <v>266</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>17</v>
@@ -6869,7 +6869,7 @@
         <v>55</v>
       </c>
       <c r="K99" s="9">
-        <v>902</v>
+        <v>525</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>17</v>
@@ -6907,7 +6907,7 @@
         <v>60</v>
       </c>
       <c r="K100" s="7">
-        <v>202</v>
+        <v>761</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>17</v>
@@ -6945,7 +6945,7 @@
         <v>50</v>
       </c>
       <c r="K101" s="9">
-        <v>539</v>
+        <v>171</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>17</v>
@@ -6983,7 +6983,7 @@
         <v>55</v>
       </c>
       <c r="K102" s="7">
-        <v>578</v>
+        <v>200</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>17</v>
@@ -7021,7 +7021,7 @@
         <v>60</v>
       </c>
       <c r="K103" s="9">
-        <v>849</v>
+        <v>553</v>
       </c>
       <c r="L103" s="8" t="s">
         <v>17</v>
@@ -7059,7 +7059,7 @@
         <v>50</v>
       </c>
       <c r="K104" s="7">
-        <v>984</v>
+        <v>350</v>
       </c>
       <c r="L104" s="8" t="s">
         <v>17</v>
@@ -7097,7 +7097,7 @@
         <v>55</v>
       </c>
       <c r="K105" s="9">
-        <v>881</v>
+        <v>625</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>17</v>
@@ -7135,7 +7135,7 @@
         <v>60</v>
       </c>
       <c r="K106" s="7">
-        <v>556</v>
+        <v>464</v>
       </c>
       <c r="L106" s="8" t="s">
         <v>17</v>
@@ -7173,7 +7173,7 @@
         <v>50</v>
       </c>
       <c r="K107" s="9">
-        <v>740</v>
+        <v>653</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>17</v>
@@ -7211,7 +7211,7 @@
         <v>55</v>
       </c>
       <c r="K108" s="7">
-        <v>774</v>
+        <v>563</v>
       </c>
       <c r="L108" s="8" t="s">
         <v>17</v>
@@ -7249,7 +7249,7 @@
         <v>60</v>
       </c>
       <c r="K109" s="9">
-        <v>441</v>
+        <v>351</v>
       </c>
       <c r="L109" s="8" t="s">
         <v>17</v>
@@ -7287,7 +7287,7 @@
         <v>50</v>
       </c>
       <c r="K110" s="7">
-        <v>209</v>
+        <v>693</v>
       </c>
       <c r="L110" s="8" t="s">
         <v>17</v>
@@ -7325,7 +7325,7 @@
         <v>55</v>
       </c>
       <c r="K111" s="9">
-        <v>848</v>
+        <v>448</v>
       </c>
       <c r="L111" s="8" t="s">
         <v>17</v>
@@ -7363,7 +7363,7 @@
         <v>60</v>
       </c>
       <c r="K112" s="7">
-        <v>986</v>
+        <v>735</v>
       </c>
       <c r="L112" s="8" t="s">
         <v>17</v>
@@ -7401,7 +7401,7 @@
         <v>50</v>
       </c>
       <c r="K113" s="9">
-        <v>252</v>
+        <v>771</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>17</v>
@@ -7439,7 +7439,7 @@
         <v>55</v>
       </c>
       <c r="K114" s="7">
-        <v>715</v>
+        <v>278</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>17</v>
@@ -7477,7 +7477,7 @@
         <v>60</v>
       </c>
       <c r="K115" s="9">
-        <v>359</v>
+        <v>916</v>
       </c>
       <c r="L115" s="8" t="s">
         <v>17</v>
@@ -7515,7 +7515,7 @@
         <v>50</v>
       </c>
       <c r="K116" s="7">
-        <v>861</v>
+        <v>1019</v>
       </c>
       <c r="L116" s="8" t="s">
         <v>17</v>
@@ -7553,7 +7553,7 @@
         <v>55</v>
       </c>
       <c r="K117" s="9">
-        <v>1039</v>
+        <v>299</v>
       </c>
       <c r="L117" s="8" t="s">
         <v>17</v>
@@ -7591,7 +7591,7 @@
         <v>60</v>
       </c>
       <c r="K118" s="7">
-        <v>941</v>
+        <v>213</v>
       </c>
       <c r="L118" s="8" t="s">
         <v>17</v>
@@ -7629,7 +7629,7 @@
         <v>50</v>
       </c>
       <c r="K119" s="9">
-        <v>594</v>
+        <v>656</v>
       </c>
       <c r="L119" s="8" t="s">
         <v>17</v>
@@ -7667,7 +7667,7 @@
         <v>55</v>
       </c>
       <c r="K120" s="7">
-        <v>722</v>
+        <v>693</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>17</v>
@@ -7705,7 +7705,7 @@
         <v>60</v>
       </c>
       <c r="K121" s="9">
-        <v>392</v>
+        <v>271</v>
       </c>
       <c r="L121" s="8" t="s">
         <v>17</v>
@@ -7743,7 +7743,7 @@
         <v>50</v>
       </c>
       <c r="K122" s="7">
-        <v>602</v>
+        <v>996</v>
       </c>
       <c r="L122" s="8" t="s">
         <v>17</v>
@@ -7781,7 +7781,7 @@
         <v>55</v>
       </c>
       <c r="K123" s="9">
-        <v>347</v>
+        <v>1037</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>17</v>
@@ -7819,7 +7819,7 @@
         <v>60</v>
       </c>
       <c r="K124" s="7">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="L124" s="8" t="s">
         <v>17</v>
@@ -7857,7 +7857,7 @@
         <v>50</v>
       </c>
       <c r="K125" s="9">
-        <v>409</v>
+        <v>338</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>17</v>
@@ -7895,7 +7895,7 @@
         <v>55</v>
       </c>
       <c r="K126" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L126" s="8" t="s">
         <v>17</v>
@@ -7933,7 +7933,7 @@
         <v>60</v>
       </c>
       <c r="K127" s="9">
-        <v>527</v>
+        <v>676</v>
       </c>
       <c r="L127" s="8" t="s">
         <v>17</v>
@@ -7971,7 +7971,7 @@
         <v>50</v>
       </c>
       <c r="K128" s="7">
-        <v>1045</v>
+        <v>913</v>
       </c>
       <c r="L128" s="8" t="s">
         <v>17</v>
@@ -8009,7 +8009,7 @@
         <v>55</v>
       </c>
       <c r="K129" s="9">
-        <v>467</v>
+        <v>418</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>17</v>
@@ -8047,7 +8047,7 @@
         <v>60</v>
       </c>
       <c r="K130" s="7">
-        <v>263</v>
+        <v>423</v>
       </c>
       <c r="L130" s="8" t="s">
         <v>17</v>
@@ -8085,7 +8085,7 @@
         <v>50</v>
       </c>
       <c r="K131" s="9">
-        <v>398</v>
+        <v>887</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>17</v>
@@ -8123,7 +8123,7 @@
         <v>55</v>
       </c>
       <c r="K132" s="7">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="L132" s="8" t="s">
         <v>17</v>
@@ -8161,7 +8161,7 @@
         <v>60</v>
       </c>
       <c r="K133" s="9">
-        <v>238</v>
+        <v>527</v>
       </c>
       <c r="L133" s="8" t="s">
         <v>17</v>
@@ -8199,7 +8199,7 @@
         <v>50</v>
       </c>
       <c r="K134" s="7">
-        <v>532</v>
+        <v>724</v>
       </c>
       <c r="L134" s="8" t="s">
         <v>17</v>
@@ -8237,7 +8237,7 @@
         <v>55</v>
       </c>
       <c r="K135" s="9">
-        <v>848</v>
+        <v>681</v>
       </c>
       <c r="L135" s="8" t="s">
         <v>17</v>
@@ -8275,7 +8275,7 @@
         <v>60</v>
       </c>
       <c r="K136" s="7">
-        <v>429</v>
+        <v>536</v>
       </c>
       <c r="L136" s="8" t="s">
         <v>17</v>
@@ -8313,7 +8313,7 @@
         <v>50</v>
       </c>
       <c r="K137" s="9">
-        <v>880</v>
+        <v>343</v>
       </c>
       <c r="L137" s="8" t="s">
         <v>17</v>
@@ -8351,7 +8351,7 @@
         <v>55</v>
       </c>
       <c r="K138" s="7">
-        <v>746</v>
+        <v>983</v>
       </c>
       <c r="L138" s="8" t="s">
         <v>17</v>
@@ -8389,7 +8389,7 @@
         <v>60</v>
       </c>
       <c r="K139" s="9">
-        <v>603</v>
+        <v>502</v>
       </c>
       <c r="L139" s="8" t="s">
         <v>17</v>
@@ -8427,7 +8427,7 @@
         <v>50</v>
       </c>
       <c r="K140" s="7">
-        <v>310</v>
+        <v>206</v>
       </c>
       <c r="L140" s="8" t="s">
         <v>17</v>
@@ -8465,7 +8465,7 @@
         <v>55</v>
       </c>
       <c r="K141" s="9">
-        <v>571</v>
+        <v>429</v>
       </c>
       <c r="L141" s="8" t="s">
         <v>17</v>
@@ -8503,7 +8503,7 @@
         <v>60</v>
       </c>
       <c r="K142" s="7">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="L142" s="10" t="s">
         <v>189</v>
@@ -8541,7 +8541,7 @@
         <v>50</v>
       </c>
       <c r="K143" s="9">
-        <v>879</v>
+        <v>495</v>
       </c>
       <c r="L143" s="8" t="s">
         <v>17</v>
@@ -8579,7 +8579,7 @@
         <v>55</v>
       </c>
       <c r="K144" s="7">
-        <v>756</v>
+        <v>331</v>
       </c>
       <c r="L144" s="8" t="s">
         <v>17</v>
@@ -8617,7 +8617,7 @@
         <v>60</v>
       </c>
       <c r="K145" s="9">
-        <v>994</v>
+        <v>709</v>
       </c>
       <c r="L145" s="8" t="s">
         <v>17</v>
@@ -8655,7 +8655,7 @@
         <v>50</v>
       </c>
       <c r="K146" s="7">
-        <v>705</v>
+        <v>363</v>
       </c>
       <c r="L146" s="8" t="s">
         <v>17</v>
@@ -8693,7 +8693,7 @@
         <v>55</v>
       </c>
       <c r="K147" s="9">
-        <v>845</v>
+        <v>890</v>
       </c>
       <c r="L147" s="8" t="s">
         <v>17</v>
@@ -8731,7 +8731,7 @@
         <v>60</v>
       </c>
       <c r="K148" s="7">
-        <v>648</v>
+        <v>692</v>
       </c>
       <c r="L148" s="8" t="s">
         <v>17</v>
@@ -8769,7 +8769,7 @@
         <v>50</v>
       </c>
       <c r="K149" s="9">
-        <v>899</v>
+        <v>501</v>
       </c>
       <c r="L149" s="8" t="s">
         <v>17</v>
@@ -8807,7 +8807,7 @@
         <v>55</v>
       </c>
       <c r="K150" s="7">
-        <v>587</v>
+        <v>334</v>
       </c>
       <c r="L150" s="8" t="s">
         <v>17</v>
@@ -8845,7 +8845,7 @@
         <v>60</v>
       </c>
       <c r="K151" s="9">
-        <v>796</v>
+        <v>247</v>
       </c>
       <c r="L151" s="8" t="s">
         <v>17</v>
@@ -8883,7 +8883,7 @@
         <v>50</v>
       </c>
       <c r="K152" s="7">
-        <v>881</v>
+        <v>789</v>
       </c>
       <c r="L152" s="8" t="s">
         <v>17</v>
@@ -8921,7 +8921,7 @@
         <v>55</v>
       </c>
       <c r="K153" s="9">
-        <v>551</v>
+        <v>292</v>
       </c>
       <c r="L153" s="8" t="s">
         <v>17</v>
@@ -8959,7 +8959,7 @@
         <v>60</v>
       </c>
       <c r="K154" s="7">
-        <v>780</v>
+        <v>328</v>
       </c>
       <c r="L154" s="8" t="s">
         <v>17</v>
@@ -8997,7 +8997,7 @@
         <v>50</v>
       </c>
       <c r="K155" s="9">
-        <v>266</v>
+        <v>644</v>
       </c>
       <c r="L155" s="8" t="s">
         <v>17</v>
@@ -9035,7 +9035,7 @@
         <v>55</v>
       </c>
       <c r="K156" s="7">
-        <v>471</v>
+        <v>158</v>
       </c>
       <c r="L156" s="8" t="s">
         <v>17</v>
@@ -9073,7 +9073,7 @@
         <v>60</v>
       </c>
       <c r="K157" s="9">
-        <v>368</v>
+        <v>550</v>
       </c>
       <c r="L157" s="8" t="s">
         <v>17</v>
@@ -9111,7 +9111,7 @@
         <v>50</v>
       </c>
       <c r="K158" s="7">
-        <v>625</v>
+        <v>729</v>
       </c>
       <c r="L158" s="8" t="s">
         <v>17</v>
@@ -9149,7 +9149,7 @@
         <v>55</v>
       </c>
       <c r="K159" s="9">
-        <v>1040</v>
+        <v>364</v>
       </c>
       <c r="L159" s="8" t="s">
         <v>17</v>
@@ -9187,7 +9187,7 @@
         <v>60</v>
       </c>
       <c r="K160" s="7">
-        <v>791</v>
+        <v>251</v>
       </c>
       <c r="L160" s="8" t="s">
         <v>17</v>
@@ -9225,7 +9225,7 @@
         <v>50</v>
       </c>
       <c r="K161" s="9">
-        <v>765</v>
+        <v>583</v>
       </c>
       <c r="L161" s="8" t="s">
         <v>17</v>
@@ -9263,7 +9263,7 @@
         <v>55</v>
       </c>
       <c r="K162" s="7">
-        <v>502</v>
+        <v>397</v>
       </c>
       <c r="L162" s="8" t="s">
         <v>17</v>
@@ -9301,7 +9301,7 @@
         <v>60</v>
       </c>
       <c r="K163" s="9">
-        <v>985</v>
+        <v>249</v>
       </c>
       <c r="L163" s="8" t="s">
         <v>17</v>
@@ -9339,7 +9339,7 @@
         <v>50</v>
       </c>
       <c r="K164" s="7">
-        <v>307</v>
+        <v>921</v>
       </c>
       <c r="L164" s="8" t="s">
         <v>17</v>
@@ -9377,7 +9377,7 @@
         <v>55</v>
       </c>
       <c r="K165" s="9">
-        <v>653</v>
+        <v>974</v>
       </c>
       <c r="L165" s="8" t="s">
         <v>17</v>
@@ -9415,7 +9415,7 @@
         <v>60</v>
       </c>
       <c r="K166" s="7">
-        <v>259</v>
+        <v>573</v>
       </c>
       <c r="L166" s="8" t="s">
         <v>17</v>
@@ -9453,7 +9453,7 @@
         <v>50</v>
       </c>
       <c r="K167" s="9">
-        <v>190</v>
+        <v>608</v>
       </c>
       <c r="L167" s="11" t="s">
         <v>267</v>
@@ -9491,7 +9491,7 @@
         <v>55</v>
       </c>
       <c r="K168" s="7">
-        <v>789</v>
+        <v>478</v>
       </c>
       <c r="L168" s="8" t="s">
         <v>17</v>
@@ -9529,7 +9529,7 @@
         <v>60</v>
       </c>
       <c r="K169" s="9">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="L169" s="8" t="s">
         <v>17</v>
@@ -9567,7 +9567,7 @@
         <v>50</v>
       </c>
       <c r="K170" s="7">
-        <v>223</v>
+        <v>945</v>
       </c>
       <c r="L170" s="8" t="s">
         <v>17</v>
@@ -9605,7 +9605,7 @@
         <v>55</v>
       </c>
       <c r="K171" s="9">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="L171" s="8" t="s">
         <v>17</v>
@@ -9643,7 +9643,7 @@
         <v>60</v>
       </c>
       <c r="K172" s="7">
-        <v>917</v>
+        <v>726</v>
       </c>
       <c r="L172" s="8" t="s">
         <v>17</v>
@@ -9681,7 +9681,7 @@
         <v>50</v>
       </c>
       <c r="K173" s="9">
-        <v>556</v>
+        <v>388</v>
       </c>
       <c r="L173" s="8" t="s">
         <v>17</v>
@@ -9719,7 +9719,7 @@
         <v>55</v>
       </c>
       <c r="K174" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="L174" s="8" t="s">
         <v>17</v>
@@ -9757,7 +9757,7 @@
         <v>60</v>
       </c>
       <c r="K175" s="9">
-        <v>609</v>
+        <v>918</v>
       </c>
       <c r="L175" s="8" t="s">
         <v>17</v>
@@ -9795,7 +9795,7 @@
         <v>50</v>
       </c>
       <c r="K176" s="7">
-        <v>342</v>
+        <v>733</v>
       </c>
       <c r="L176" s="8" t="s">
         <v>17</v>
@@ -9833,7 +9833,7 @@
         <v>55</v>
       </c>
       <c r="K177" s="9">
-        <v>733</v>
+        <v>535</v>
       </c>
       <c r="L177" s="8" t="s">
         <v>17</v>
@@ -9871,7 +9871,7 @@
         <v>60</v>
       </c>
       <c r="K178" s="7">
-        <v>215</v>
+        <v>1033</v>
       </c>
       <c r="L178" s="8" t="s">
         <v>17</v>
@@ -9909,7 +9909,7 @@
         <v>50</v>
       </c>
       <c r="K179" s="9">
-        <v>364</v>
+        <v>518</v>
       </c>
       <c r="L179" s="8" t="s">
         <v>17</v>
@@ -9947,7 +9947,7 @@
         <v>55</v>
       </c>
       <c r="K180" s="7">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L180" s="8" t="s">
         <v>17</v>
@@ -9985,7 +9985,7 @@
         <v>60</v>
       </c>
       <c r="K181" s="9">
-        <v>827</v>
+        <v>352</v>
       </c>
       <c r="L181" s="8" t="s">
         <v>17</v>
@@ -10023,7 +10023,7 @@
         <v>50</v>
       </c>
       <c r="K182" s="7">
-        <v>881</v>
+        <v>954</v>
       </c>
       <c r="L182" s="8" t="s">
         <v>17</v>
@@ -10061,7 +10061,7 @@
         <v>55</v>
       </c>
       <c r="K183" s="9">
-        <v>611</v>
+        <v>236</v>
       </c>
       <c r="L183" s="8" t="s">
         <v>17</v>
@@ -10099,7 +10099,7 @@
         <v>60</v>
       </c>
       <c r="K184" s="7">
-        <v>395</v>
+        <v>328</v>
       </c>
       <c r="L184" s="8" t="s">
         <v>17</v>
@@ -10137,7 +10137,7 @@
         <v>50</v>
       </c>
       <c r="K185" s="9">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="L185" s="8" t="s">
         <v>17</v>
@@ -10175,7 +10175,7 @@
         <v>55</v>
       </c>
       <c r="K186" s="7">
-        <v>202</v>
+        <v>538</v>
       </c>
       <c r="L186" s="8" t="s">
         <v>17</v>
@@ -10213,7 +10213,7 @@
         <v>60</v>
       </c>
       <c r="K187" s="9">
-        <v>512</v>
+        <v>844</v>
       </c>
       <c r="L187" s="8" t="s">
         <v>17</v>
@@ -10251,7 +10251,7 @@
         <v>50</v>
       </c>
       <c r="K188" s="7">
-        <v>1005</v>
+        <v>506</v>
       </c>
       <c r="L188" s="8" t="s">
         <v>17</v>
@@ -10289,7 +10289,7 @@
         <v>55</v>
       </c>
       <c r="K189" s="9">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="L189" s="10" t="s">
         <v>189</v>
@@ -10327,7 +10327,7 @@
         <v>60</v>
       </c>
       <c r="K190" s="7">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="L190" s="8" t="s">
         <v>17</v>
@@ -10365,7 +10365,7 @@
         <v>50</v>
       </c>
       <c r="K191" s="9">
-        <v>220</v>
+        <v>820</v>
       </c>
       <c r="L191" s="8" t="s">
         <v>17</v>
@@ -10403,7 +10403,7 @@
         <v>55</v>
       </c>
       <c r="K192" s="7">
-        <v>799</v>
+        <v>1043</v>
       </c>
       <c r="L192" s="8" t="s">
         <v>17</v>
@@ -10441,7 +10441,7 @@
         <v>60</v>
       </c>
       <c r="K193" s="9">
-        <v>714</v>
+        <v>173</v>
       </c>
       <c r="L193" s="8" t="s">
         <v>17</v>
@@ -10479,7 +10479,7 @@
         <v>50</v>
       </c>
       <c r="K194" s="7">
-        <v>542</v>
+        <v>1039</v>
       </c>
       <c r="L194" s="8" t="s">
         <v>17</v>
@@ -10517,7 +10517,7 @@
         <v>55</v>
       </c>
       <c r="K195" s="9">
-        <v>576</v>
+        <v>636</v>
       </c>
       <c r="L195" s="8" t="s">
         <v>17</v>
@@ -10555,7 +10555,7 @@
         <v>60</v>
       </c>
       <c r="K196" s="7">
-        <v>289</v>
+        <v>603</v>
       </c>
       <c r="L196" s="8" t="s">
         <v>17</v>
@@ -10593,7 +10593,7 @@
         <v>50</v>
       </c>
       <c r="K197" s="9">
-        <v>544</v>
+        <v>1015</v>
       </c>
       <c r="L197" s="8" t="s">
         <v>17</v>
@@ -10631,7 +10631,7 @@
         <v>55</v>
       </c>
       <c r="K198" s="7">
-        <v>560</v>
+        <v>421</v>
       </c>
       <c r="L198" s="8" t="s">
         <v>17</v>
@@ -10669,7 +10669,7 @@
         <v>60</v>
       </c>
       <c r="K199" s="9">
-        <v>954</v>
+        <v>352</v>
       </c>
       <c r="L199" s="8" t="s">
         <v>17</v>
@@ -10707,7 +10707,7 @@
         <v>50</v>
       </c>
       <c r="K200" s="7">
-        <v>680</v>
+        <v>476</v>
       </c>
       <c r="L200" s="8" t="s">
         <v>17</v>
@@ -10745,7 +10745,7 @@
         <v>55</v>
       </c>
       <c r="K201" s="9">
-        <v>530</v>
+        <v>679</v>
       </c>
       <c r="L201" s="8" t="s">
         <v>17</v>
@@ -10783,7 +10783,7 @@
         <v>60</v>
       </c>
       <c r="K202" s="7">
-        <v>470</v>
+        <v>948</v>
       </c>
       <c r="L202" s="8" t="s">
         <v>17</v>
@@ -10821,7 +10821,7 @@
         <v>50</v>
       </c>
       <c r="K203" s="9">
-        <v>736</v>
+        <v>217</v>
       </c>
       <c r="L203" s="8" t="s">
         <v>17</v>
@@ -10859,7 +10859,7 @@
         <v>55</v>
       </c>
       <c r="K204" s="7">
-        <v>601</v>
+        <v>650</v>
       </c>
       <c r="L204" s="8" t="s">
         <v>17</v>
@@ -10897,7 +10897,7 @@
         <v>60</v>
       </c>
       <c r="K205" s="9">
-        <v>745</v>
+        <v>542</v>
       </c>
       <c r="L205" s="8" t="s">
         <v>17</v>
@@ -10935,7 +10935,7 @@
         <v>50</v>
       </c>
       <c r="K206" s="7">
-        <v>280</v>
+        <v>718</v>
       </c>
       <c r="L206" s="8" t="s">
         <v>17</v>
@@ -10973,7 +10973,7 @@
         <v>55</v>
       </c>
       <c r="K207" s="9">
-        <v>344</v>
+        <v>218</v>
       </c>
       <c r="L207" s="8" t="s">
         <v>17</v>
@@ -11011,7 +11011,7 @@
         <v>60</v>
       </c>
       <c r="K208" s="7">
-        <v>641</v>
+        <v>765</v>
       </c>
       <c r="L208" s="8" t="s">
         <v>17</v>
@@ -11049,7 +11049,7 @@
         <v>50</v>
       </c>
       <c r="K209" s="9">
-        <v>377</v>
+        <v>529</v>
       </c>
       <c r="L209" s="8" t="s">
         <v>17</v>
@@ -11087,7 +11087,7 @@
         <v>55</v>
       </c>
       <c r="K210" s="7">
-        <v>543</v>
+        <v>193</v>
       </c>
       <c r="L210" s="8" t="s">
         <v>17</v>
@@ -11125,7 +11125,7 @@
         <v>60</v>
       </c>
       <c r="K211" s="9">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="L211" s="8" t="s">
         <v>17</v>
@@ -11163,7 +11163,7 @@
         <v>50</v>
       </c>
       <c r="K212" s="7">
-        <v>506</v>
+        <v>189</v>
       </c>
       <c r="L212" s="8" t="s">
         <v>17</v>
@@ -11201,7 +11201,7 @@
         <v>55</v>
       </c>
       <c r="K213" s="9">
-        <v>751</v>
+        <v>925</v>
       </c>
       <c r="L213" s="8" t="s">
         <v>17</v>
@@ -11239,7 +11239,7 @@
         <v>60</v>
       </c>
       <c r="K214" s="7">
-        <v>218</v>
+        <v>359</v>
       </c>
       <c r="L214" s="8" t="s">
         <v>17</v>
@@ -11277,7 +11277,7 @@
         <v>50</v>
       </c>
       <c r="K215" s="9">
-        <v>729</v>
+        <v>556</v>
       </c>
       <c r="L215" s="8" t="s">
         <v>17</v>
@@ -11315,7 +11315,7 @@
         <v>55</v>
       </c>
       <c r="K216" s="7">
-        <v>395</v>
+        <v>209</v>
       </c>
       <c r="L216" s="8" t="s">
         <v>17</v>
@@ -11353,7 +11353,7 @@
         <v>60</v>
       </c>
       <c r="K217" s="9">
-        <v>223</v>
+        <v>429</v>
       </c>
       <c r="L217" s="8" t="s">
         <v>17</v>
@@ -11391,7 +11391,7 @@
         <v>50</v>
       </c>
       <c r="K218" s="7">
-        <v>436</v>
+        <v>989</v>
       </c>
       <c r="L218" s="8" t="s">
         <v>17</v>
@@ -11429,7 +11429,7 @@
         <v>55</v>
       </c>
       <c r="K219" s="9">
-        <v>1006</v>
+        <v>627</v>
       </c>
       <c r="L219" s="8" t="s">
         <v>17</v>
@@ -11467,7 +11467,7 @@
         <v>60</v>
       </c>
       <c r="K220" s="7">
-        <v>824</v>
+        <v>227</v>
       </c>
       <c r="L220" s="8" t="s">
         <v>17</v>
@@ -11505,7 +11505,7 @@
         <v>50</v>
       </c>
       <c r="K221" s="9">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="L221" s="8" t="s">
         <v>17</v>
@@ -11543,7 +11543,7 @@
         <v>55</v>
       </c>
       <c r="K222" s="7">
-        <v>752</v>
+        <v>725</v>
       </c>
       <c r="L222" s="8" t="s">
         <v>17</v>
@@ -11581,7 +11581,7 @@
         <v>60</v>
       </c>
       <c r="K223" s="9">
-        <v>953</v>
+        <v>385</v>
       </c>
       <c r="L223" s="8" t="s">
         <v>17</v>
@@ -11619,7 +11619,7 @@
         <v>50</v>
       </c>
       <c r="K224" s="7">
-        <v>358</v>
+        <v>865</v>
       </c>
       <c r="L224" s="8" t="s">
         <v>17</v>
@@ -11657,7 +11657,7 @@
         <v>55</v>
       </c>
       <c r="K225" s="9">
-        <v>190</v>
+        <v>781</v>
       </c>
       <c r="L225" s="8" t="s">
         <v>17</v>
@@ -11695,7 +11695,7 @@
         <v>60</v>
       </c>
       <c r="K226" s="7">
-        <v>805</v>
+        <v>935</v>
       </c>
       <c r="L226" s="8" t="s">
         <v>17</v>
@@ -11733,7 +11733,7 @@
         <v>50</v>
       </c>
       <c r="K227" s="9">
-        <v>953</v>
+        <v>645</v>
       </c>
       <c r="L227" s="8" t="s">
         <v>17</v>
@@ -11771,7 +11771,7 @@
         <v>55</v>
       </c>
       <c r="K228" s="7">
-        <v>1016</v>
+        <v>511</v>
       </c>
       <c r="L228" s="8" t="s">
         <v>17</v>
@@ -11809,7 +11809,7 @@
         <v>60</v>
       </c>
       <c r="K229" s="9">
-        <v>268</v>
+        <v>603</v>
       </c>
       <c r="L229" s="8" t="s">
         <v>17</v>
@@ -11847,7 +11847,7 @@
         <v>50</v>
       </c>
       <c r="K230" s="7">
-        <v>303</v>
+        <v>833</v>
       </c>
       <c r="L230" s="8" t="s">
         <v>17</v>
@@ -11885,7 +11885,7 @@
         <v>55</v>
       </c>
       <c r="K231" s="9">
-        <v>471</v>
+        <v>854</v>
       </c>
       <c r="L231" s="8" t="s">
         <v>17</v>
@@ -11923,7 +11923,7 @@
         <v>60</v>
       </c>
       <c r="K232" s="7">
-        <v>491</v>
+        <v>749</v>
       </c>
       <c r="L232" s="8" t="s">
         <v>17</v>
@@ -11961,7 +11961,7 @@
         <v>50</v>
       </c>
       <c r="K233" s="9">
-        <v>978</v>
+        <v>392</v>
       </c>
       <c r="L233" s="8" t="s">
         <v>17</v>
@@ -11999,7 +11999,7 @@
         <v>55</v>
       </c>
       <c r="K234" s="7">
-        <v>739</v>
+        <v>627</v>
       </c>
       <c r="L234" s="8" t="s">
         <v>17</v>
@@ -12037,7 +12037,7 @@
         <v>60</v>
       </c>
       <c r="K235" s="9">
-        <v>661</v>
+        <v>173</v>
       </c>
       <c r="L235" s="8" t="s">
         <v>17</v>
@@ -12075,7 +12075,7 @@
         <v>50</v>
       </c>
       <c r="K236" s="7">
-        <v>997</v>
+        <v>527</v>
       </c>
       <c r="L236" s="10" t="s">
         <v>189</v>
@@ -12113,7 +12113,7 @@
         <v>55</v>
       </c>
       <c r="K237" s="9">
-        <v>446</v>
+        <v>1009</v>
       </c>
       <c r="L237" s="8" t="s">
         <v>17</v>
@@ -12151,7 +12151,7 @@
         <v>60</v>
       </c>
       <c r="K238" s="7">
-        <v>802</v>
+        <v>1026</v>
       </c>
       <c r="L238" s="8" t="s">
         <v>17</v>
@@ -12189,7 +12189,7 @@
         <v>50</v>
       </c>
       <c r="K239" s="9">
-        <v>512</v>
+        <v>567</v>
       </c>
       <c r="L239" s="8" t="s">
         <v>17</v>
@@ -12227,7 +12227,7 @@
         <v>55</v>
       </c>
       <c r="K240" s="7">
-        <v>731</v>
+        <v>359</v>
       </c>
       <c r="L240" s="8" t="s">
         <v>17</v>
@@ -12265,7 +12265,7 @@
         <v>60</v>
       </c>
       <c r="K241" s="9">
-        <v>861</v>
+        <v>745</v>
       </c>
       <c r="L241" s="8" t="s">
         <v>17</v>
@@ -12303,7 +12303,7 @@
         <v>50</v>
       </c>
       <c r="K242" s="7">
-        <v>1023</v>
+        <v>233</v>
       </c>
       <c r="L242" s="8" t="s">
         <v>17</v>
@@ -12341,7 +12341,7 @@
         <v>55</v>
       </c>
       <c r="K243" s="9">
-        <v>359</v>
+        <v>534</v>
       </c>
       <c r="L243" s="8" t="s">
         <v>17</v>
@@ -12379,7 +12379,7 @@
         <v>60</v>
       </c>
       <c r="K244" s="7">
-        <v>811</v>
+        <v>548</v>
       </c>
       <c r="L244" s="8" t="s">
         <v>17</v>
@@ -12417,7 +12417,7 @@
         <v>50</v>
       </c>
       <c r="K245" s="9">
-        <v>681</v>
+        <v>483</v>
       </c>
       <c r="L245" s="8" t="s">
         <v>17</v>
@@ -12455,7 +12455,7 @@
         <v>55</v>
       </c>
       <c r="K246" s="7">
-        <v>738</v>
+        <v>499</v>
       </c>
       <c r="L246" s="8" t="s">
         <v>17</v>
@@ -12493,7 +12493,7 @@
         <v>60</v>
       </c>
       <c r="K247" s="9">
-        <v>518</v>
+        <v>685</v>
       </c>
       <c r="L247" s="8" t="s">
         <v>17</v>
@@ -12531,7 +12531,7 @@
         <v>50</v>
       </c>
       <c r="K248" s="7">
-        <v>628</v>
+        <v>169</v>
       </c>
       <c r="L248" s="8" t="s">
         <v>17</v>
@@ -12569,7 +12569,7 @@
         <v>55</v>
       </c>
       <c r="K249" s="9">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="L249" s="8" t="s">
         <v>17</v>
@@ -12607,7 +12607,7 @@
         <v>60</v>
       </c>
       <c r="K250" s="7">
-        <v>755</v>
+        <v>516</v>
       </c>
       <c r="L250" s="11" t="s">
         <v>267</v>
@@ -12645,7 +12645,7 @@
         <v>50</v>
       </c>
       <c r="K251" s="9">
-        <v>703</v>
+        <v>245</v>
       </c>
       <c r="L251" s="8" t="s">
         <v>17</v>
@@ -12683,7 +12683,7 @@
         <v>55</v>
       </c>
       <c r="K252" s="7">
-        <v>388</v>
+        <v>614</v>
       </c>
       <c r="L252" s="8" t="s">
         <v>17</v>
@@ -12721,7 +12721,7 @@
         <v>60</v>
       </c>
       <c r="K253" s="9">
-        <v>930</v>
+        <v>424</v>
       </c>
       <c r="L253" s="8" t="s">
         <v>17</v>
@@ -12759,7 +12759,7 @@
         <v>50</v>
       </c>
       <c r="K254" s="7">
-        <v>787</v>
+        <v>203</v>
       </c>
       <c r="L254" s="8" t="s">
         <v>17</v>
@@ -12797,7 +12797,7 @@
         <v>55</v>
       </c>
       <c r="K255" s="9">
-        <v>346</v>
+        <v>679</v>
       </c>
       <c r="L255" s="8" t="s">
         <v>17</v>
@@ -12835,7 +12835,7 @@
         <v>60</v>
       </c>
       <c r="K256" s="7">
-        <v>786</v>
+        <v>393</v>
       </c>
       <c r="L256" s="8" t="s">
         <v>17</v>
@@ -12873,7 +12873,7 @@
         <v>50</v>
       </c>
       <c r="K257" s="9">
-        <v>800</v>
+        <v>592</v>
       </c>
       <c r="L257" s="8" t="s">
         <v>17</v>
@@ -12911,7 +12911,7 @@
         <v>55</v>
       </c>
       <c r="K258" s="7">
-        <v>735</v>
+        <v>470</v>
       </c>
       <c r="L258" s="8" t="s">
         <v>17</v>
@@ -12949,7 +12949,7 @@
         <v>60</v>
       </c>
       <c r="K259" s="9">
-        <v>744</v>
+        <v>295</v>
       </c>
       <c r="L259" s="8" t="s">
         <v>17</v>
@@ -12987,7 +12987,7 @@
         <v>50</v>
       </c>
       <c r="K260" s="7">
-        <v>948</v>
+        <v>675</v>
       </c>
       <c r="L260" s="8" t="s">
         <v>17</v>
@@ -13025,7 +13025,7 @@
         <v>55</v>
       </c>
       <c r="K261" s="9">
-        <v>729</v>
+        <v>489</v>
       </c>
       <c r="L261" s="8" t="s">
         <v>17</v>
@@ -13063,7 +13063,7 @@
         <v>60</v>
       </c>
       <c r="K262" s="7">
-        <v>414</v>
+        <v>282</v>
       </c>
       <c r="L262" s="8" t="s">
         <v>17</v>
@@ -13101,7 +13101,7 @@
         <v>50</v>
       </c>
       <c r="K263" s="9">
-        <v>451</v>
+        <v>643</v>
       </c>
       <c r="L263" s="8" t="s">
         <v>17</v>
@@ -13139,7 +13139,7 @@
         <v>55</v>
       </c>
       <c r="K264" s="7">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="L264" s="8" t="s">
         <v>17</v>
@@ -13177,7 +13177,7 @@
         <v>60</v>
       </c>
       <c r="K265" s="9">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="L265" s="8" t="s">
         <v>17</v>
@@ -13215,7 +13215,7 @@
         <v>50</v>
       </c>
       <c r="K266" s="7">
-        <v>719</v>
+        <v>871</v>
       </c>
       <c r="L266" s="8" t="s">
         <v>17</v>
@@ -13253,7 +13253,7 @@
         <v>55</v>
       </c>
       <c r="K267" s="9">
-        <v>444</v>
+        <v>152</v>
       </c>
       <c r="L267" s="8" t="s">
         <v>17</v>
@@ -13291,7 +13291,7 @@
         <v>60</v>
       </c>
       <c r="K268" s="7">
-        <v>611</v>
+        <v>196</v>
       </c>
       <c r="L268" s="8" t="s">
         <v>17</v>
@@ -13329,7 +13329,7 @@
         <v>50</v>
       </c>
       <c r="K269" s="9">
-        <v>515</v>
+        <v>975</v>
       </c>
       <c r="L269" s="8" t="s">
         <v>17</v>
@@ -13367,7 +13367,7 @@
         <v>55</v>
       </c>
       <c r="K270" s="7">
-        <v>749</v>
+        <v>473</v>
       </c>
       <c r="L270" s="8" t="s">
         <v>17</v>
@@ -13405,7 +13405,7 @@
         <v>60</v>
       </c>
       <c r="K271" s="9">
-        <v>697</v>
+        <v>812</v>
       </c>
       <c r="L271" s="8" t="s">
         <v>17</v>
@@ -13443,7 +13443,7 @@
         <v>50</v>
       </c>
       <c r="K272" s="7">
-        <v>532</v>
+        <v>314</v>
       </c>
       <c r="L272" s="8" t="s">
         <v>17</v>
@@ -13481,7 +13481,7 @@
         <v>55</v>
       </c>
       <c r="K273" s="9">
-        <v>521</v>
+        <v>585</v>
       </c>
       <c r="L273" s="8" t="s">
         <v>17</v>
@@ -13519,7 +13519,7 @@
         <v>60</v>
       </c>
       <c r="K274" s="7">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="L274" s="8" t="s">
         <v>17</v>
@@ -13557,7 +13557,7 @@
         <v>50</v>
       </c>
       <c r="K275" s="9">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="L275" s="8" t="s">
         <v>17</v>
@@ -13595,7 +13595,7 @@
         <v>55</v>
       </c>
       <c r="K276" s="7">
-        <v>1023</v>
+        <v>857</v>
       </c>
       <c r="L276" s="8" t="s">
         <v>17</v>
@@ -13633,7 +13633,7 @@
         <v>60</v>
       </c>
       <c r="K277" s="9">
-        <v>160</v>
+        <v>945</v>
       </c>
       <c r="L277" s="8" t="s">
         <v>17</v>
@@ -13671,7 +13671,7 @@
         <v>50</v>
       </c>
       <c r="K278" s="7">
-        <v>1043</v>
+        <v>1021</v>
       </c>
       <c r="L278" s="8" t="s">
         <v>17</v>
@@ -13709,7 +13709,7 @@
         <v>55</v>
       </c>
       <c r="K279" s="9">
-        <v>514</v>
+        <v>570</v>
       </c>
       <c r="L279" s="8" t="s">
         <v>17</v>
@@ -13747,7 +13747,7 @@
         <v>60</v>
       </c>
       <c r="K280" s="7">
-        <v>498</v>
+        <v>658</v>
       </c>
       <c r="L280" s="8" t="s">
         <v>17</v>
@@ -13785,7 +13785,7 @@
         <v>50</v>
       </c>
       <c r="K281" s="9">
-        <v>242</v>
+        <v>156</v>
       </c>
       <c r="L281" s="8" t="s">
         <v>17</v>
@@ -13823,7 +13823,7 @@
         <v>55</v>
       </c>
       <c r="K282" s="7">
-        <v>387</v>
+        <v>940</v>
       </c>
       <c r="L282" s="8" t="s">
         <v>17</v>
@@ -13861,7 +13861,7 @@
         <v>60</v>
       </c>
       <c r="K283" s="9">
-        <v>1041</v>
+        <v>819</v>
       </c>
       <c r="L283" s="10" t="s">
         <v>189</v>
@@ -13899,7 +13899,7 @@
         <v>50</v>
       </c>
       <c r="K284" s="7">
-        <v>635</v>
+        <v>384</v>
       </c>
       <c r="L284" s="8" t="s">
         <v>17</v>
@@ -13937,7 +13937,7 @@
         <v>55</v>
       </c>
       <c r="K285" s="9">
-        <v>908</v>
+        <v>735</v>
       </c>
       <c r="L285" s="8" t="s">
         <v>17</v>
@@ -13975,7 +13975,7 @@
         <v>60</v>
       </c>
       <c r="K286" s="7">
-        <v>619</v>
+        <v>1007</v>
       </c>
       <c r="L286" s="8" t="s">
         <v>17</v>
@@ -14013,7 +14013,7 @@
         <v>50</v>
       </c>
       <c r="K287" s="9">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="L287" s="8" t="s">
         <v>17</v>
@@ -14051,7 +14051,7 @@
         <v>55</v>
       </c>
       <c r="K288" s="7">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="L288" s="8" t="s">
         <v>17</v>
@@ -14089,7 +14089,7 @@
         <v>60</v>
       </c>
       <c r="K289" s="9">
-        <v>584</v>
+        <v>707</v>
       </c>
       <c r="L289" s="8" t="s">
         <v>17</v>
@@ -14127,7 +14127,7 @@
         <v>50</v>
       </c>
       <c r="K290" s="7">
-        <v>314</v>
+        <v>902</v>
       </c>
       <c r="L290" s="8" t="s">
         <v>17</v>
@@ -14165,7 +14165,7 @@
         <v>55</v>
       </c>
       <c r="K291" s="9">
-        <v>909</v>
+        <v>530</v>
       </c>
       <c r="L291" s="8" t="s">
         <v>17</v>
@@ -14203,7 +14203,7 @@
         <v>60</v>
       </c>
       <c r="K292" s="7">
-        <v>657</v>
+        <v>394</v>
       </c>
       <c r="L292" s="8" t="s">
         <v>17</v>
@@ -14241,7 +14241,7 @@
         <v>50</v>
       </c>
       <c r="K293" s="9">
-        <v>344</v>
+        <v>1035</v>
       </c>
       <c r="L293" s="8" t="s">
         <v>17</v>
@@ -14279,7 +14279,7 @@
         <v>55</v>
       </c>
       <c r="K294" s="7">
-        <v>323</v>
+        <v>500</v>
       </c>
       <c r="L294" s="8" t="s">
         <v>17</v>
@@ -14317,7 +14317,7 @@
         <v>60</v>
       </c>
       <c r="K295" s="9">
-        <v>183</v>
+        <v>432</v>
       </c>
       <c r="L295" s="8" t="s">
         <v>17</v>
@@ -14355,7 +14355,7 @@
         <v>50</v>
       </c>
       <c r="K296" s="7">
-        <v>994</v>
+        <v>849</v>
       </c>
       <c r="L296" s="8" t="s">
         <v>17</v>
@@ -14393,7 +14393,7 @@
         <v>55</v>
       </c>
       <c r="K297" s="9">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="L297" s="8" t="s">
         <v>17</v>
@@ -14431,7 +14431,7 @@
         <v>60</v>
       </c>
       <c r="K298" s="7">
-        <v>604</v>
+        <v>150</v>
       </c>
       <c r="L298" s="8" t="s">
         <v>17</v>
@@ -14469,7 +14469,7 @@
         <v>50</v>
       </c>
       <c r="K299" s="9">
-        <v>345</v>
+        <v>489</v>
       </c>
       <c r="L299" s="8" t="s">
         <v>17</v>
@@ -14507,7 +14507,7 @@
         <v>55</v>
       </c>
       <c r="K300" s="7">
-        <v>539</v>
+        <v>911</v>
       </c>
       <c r="L300" s="8" t="s">
         <v>17</v>
@@ -14545,7 +14545,7 @@
         <v>60</v>
       </c>
       <c r="K301" s="9">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="L301" s="8" t="s">
         <v>17</v>
@@ -14583,7 +14583,7 @@
         <v>50</v>
       </c>
       <c r="K302" s="7">
-        <v>240</v>
+        <v>592</v>
       </c>
       <c r="L302" s="8" t="s">
         <v>17</v>
@@ -14621,7 +14621,7 @@
         <v>55</v>
       </c>
       <c r="K303" s="9">
-        <v>577</v>
+        <v>248</v>
       </c>
       <c r="L303" s="8" t="s">
         <v>17</v>
@@ -14659,7 +14659,7 @@
         <v>60</v>
       </c>
       <c r="K304" s="7">
-        <v>1014</v>
+        <v>367</v>
       </c>
       <c r="L304" s="8" t="s">
         <v>17</v>
@@ -14697,7 +14697,7 @@
         <v>50</v>
       </c>
       <c r="K305" s="9">
-        <v>527</v>
+        <v>844</v>
       </c>
       <c r="L305" s="8" t="s">
         <v>17</v>
@@ -14735,7 +14735,7 @@
         <v>55</v>
       </c>
       <c r="K306" s="7">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="L306" s="8" t="s">
         <v>17</v>
